--- a/outputs/q3/q3_pareto.xlsx
+++ b/outputs/q3/q3_pareto.xlsx
@@ -537,7 +537,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Q3-BASE-ENERGY</t>
+          <t>Q3-SEED-20260927</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -547,31 +547,31 @@
         <v>0</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>7368.139148248344</v>
+        <v>6975.244356990602</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>78.47952449430414</v>
+        <v>76.7409755788635</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>3.599901242305765</v>
+        <v>3.348637801016601</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>82.07942573660991</v>
+        <v>80.08961337988009</v>
       </c>
       <c r="H2" t="n">
         <v>26</v>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>23655.43013907938</v>
+        <v>23544.64892563613</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>18445.15442988898</v>
+        <v>17531.77729781853</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
